--- a/artfynd/A 42446-2024 artfynd.xlsx
+++ b/artfynd/A 42446-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>71793434</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425843.1887325599</v>
+        <v>425843</v>
       </c>
       <c r="R2" t="n">
-        <v>6641515.735755054</v>
+        <v>6641516</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2018-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,218 +777,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>115121809</v>
-      </c>
-      <c r="B3" t="n">
-        <v>96822</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220250</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Strutbräken</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Matteuccia struthiopteris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Lidgården, V om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>425826</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6641545</v>
-      </c>
-      <c r="S3" t="n">
-        <v>75</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hagfors</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Sunnemo</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2018-06-09</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2018-06-09</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Gunnar Flygh, Pär Dahlström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Värmlands Flora</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>115121808</v>
-      </c>
-      <c r="B4" t="n">
-        <v>102776</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>222395</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dvärghäxört</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Circaea alpina</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Lidgården, V om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>425826</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6641545</v>
-      </c>
-      <c r="S4" t="n">
-        <v>75</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Hagfors</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Sunnemo</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2018-06-09</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2018-06-09</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Gunnar Flygh, Pär Dahlström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Värmlands Flora</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42446-2024 artfynd.xlsx
+++ b/artfynd/A 42446-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,8 +782,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71793434</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>